--- a/SOT_results/SOT_60deg.xlsx
+++ b/SOT_results/SOT_60deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>60° 模型数据（52点）</a:t>
+              <a:t>60° 模型数据（角度相关形状，52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -181,7 +181,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$2:$A$53</f>
+              <f>'Sheet1'!$A$2:$A$27</f>
             </numRef>
           </xVal>
           <yVal>
@@ -605,7 +605,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.3303635682898697</v>
+        <v>-0.5039641267274426</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4251319293885958</v>
+        <v>-0.5093984924204307</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4318411938911482</v>
+        <v>-0.5172874305507262</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4335185100168002</v>
+        <v>-0.5185488521780146</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.4310025358283407</v>
+        <v>-0.506655821282364</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4351958261424336</v>
+        <v>-0.4932843212412745</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4368731422680857</v>
+        <v>-0.4805465295209971</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4268092455142293</v>
+        <v>-0.4749331099005129</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4351958261424336</v>
+        <v>-0.4667630804392562</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4150680326347395</v>
+        <v>-0.4538411263848844</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4226159552001364</v>
+        <v>-0.4486411623462382</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4310025358283407</v>
+        <v>-0.4472393980765773</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4259705874514033</v>
+        <v>-0.4476664842523243</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4276479035770553</v>
+        <v>-0.4492842253968948</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4167453487603915</v>
+        <v>-0.4658176682244434</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4100360842578205</v>
+        <v>-0.5258628711528431</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4167453487603915</v>
+        <v>-0.5237722107787219</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.4108747423206466</v>
+        <v>-0.5254910416570647</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.406681452006535</v>
+        <v>-0.521234070889021</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.41255205844628</v>
+        <v>-0.5103016256311537</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.405842793943709</v>
+        <v>-0.5054368279009545</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.4016495036296162</v>
+        <v>-0.5382165682701892</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.3848763423732074</v>
+        <v>-0.5142862349093876</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.3102357747821755</v>
+        <v>-0.5968184289838053</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>0.003422340712709027</v>
+        <v>-0.7127857314199553</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3606906754742488</v>
+        <v>-0.9601654374792454</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2239894112345008</v>
+        <v>0.7315266803331284</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2902433981973284</v>
+        <v>0.6324362647882658</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3095325336421966</v>
+        <v>0.5862784234552012</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3539814109716778</v>
+        <v>0.3763281536602175</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3506267787203924</v>
+        <v>0.3796352427385145</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3539814109716778</v>
+        <v>0.3514905684279914</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3715932302909126</v>
+        <v>0.3436730814091082</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3648839657883417</v>
+        <v>0.3348289715075891</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3766251786678315</v>
+        <v>0.3331893234998242</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.333947974545635</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3749478625421981</v>
+        <v>0.3344172645781615</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>0.386689075421688</v>
+        <v>0.3350769404617849</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.3353766193246073</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4294606366255358</v>
+        <v>0.3353746917663612</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>0.3925596818614329</v>
+        <v>0.3355154467042921</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3975916302383518</v>
+        <v>0.3357487890335164</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3992689463639852</v>
+        <v>0.3433100674593284</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3975916302383518</v>
+        <v>0.3344592131218199</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3992689463639852</v>
+        <v>0.3230732241042686</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3950756560498923</v>
+        <v>0.3198989150893806</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3933983399242403</v>
+        <v>0.3302405053998392</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3984302883011778</v>
+        <v>0.4050345750712405</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3816571270447691</v>
+        <v>0.2784337529939935</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2977913207627067</v>
+        <v>0.7572079601207087</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.1458587944693549</v>
+        <v>0.9956878531071215</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.6096367032091107</v>
+        <v>1.126121971149564</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,84 +1144,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>电阻单位</t>
+          <t>翻转幅度A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>沿用原始文件数值；原始文件未注明纵轴单位</t>
+          <t>0.8122403338（保持前次角度模型）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>翻转幅度A</t>
+          <t>曲线形状</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.8122403338（按前次分析的平台差模型）</t>
+          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中心基线</t>
+          <t>形状插值</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.01356048506（由已测角度基线保形插值，仅用于保持绘图尺度）</t>
+          <t>45°→75°线性混合</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>纵轴单位</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复用165°实测回线的两支路形状，按目标角度A缩放；未添加随机噪声</t>
+          <t>原始文件未注明，保留原始数值尺度</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>模型规律</t>
+          <t>实测区分</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0–90°单峰角度依赖；采用0°/45°/75°/90°实测幅度锚点的保形插值</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>实测区分</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>本文件不是该角度的实测记录；15°、30°、60°原始文件夹无实测数据，0°和45°文件也已按52点序列重新模型化</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>输入模板</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>165度.xlsx（用户上传）</t>
+          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
         </is>
       </c>
     </row>

--- a/SOT_results/SOT_60deg.xlsx
+++ b/SOT_results/SOT_60deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>60° 模型数据（角度相关形状，52点）</a:t>
+              <a:t>60° 标准双支路SOT模型（52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5039641267274426</v>
+        <v>-0.4196801668999999</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5093984924204307</v>
+        <v>-0.4196801668999992</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.5172874305507262</v>
+        <v>-0.4196801668999955</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.5185488521780146</v>
+        <v>-0.4196801668999766</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.506655821282364</v>
+        <v>-0.4196801668998785</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4932843212412745</v>
+        <v>-0.419680166899369</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4805465295209971</v>
+        <v>-0.419680166896724</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4749331099005129</v>
+        <v>-0.4196801668829919</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4667630804392562</v>
+        <v>-0.4196801668116988</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4538411263848844</v>
+        <v>-0.4196801664415676</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4486411623462382</v>
+        <v>-0.4196801645199623</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4472393980765773</v>
+        <v>-0.4196801545435873</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4476664842523243</v>
+        <v>-0.4196801027493685</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4492842253968948</v>
+        <v>-0.4196798338500667</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4658176682244434</v>
+        <v>-0.4196784378117364</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.5258628711528431</v>
+        <v>-0.4196711900938659</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.5237722107787219</v>
+        <v>-0.4196335642851063</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.5254910416570647</v>
+        <v>-0.4194382788524134</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.521234070889021</v>
+        <v>-0.4184259253723688</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.5103016256311537</v>
+        <v>-0.4132104133926276</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.5054368279009545</v>
+        <v>-0.3871764651505178</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.5382165682701892</v>
+        <v>-0.275171083350183</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.5142862349093876</v>
+        <v>0.01007290026168889</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5968184289838053</v>
+        <v>0.2736942716812417</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.7127857314199553</v>
+        <v>0.3665970648816554</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.9601654374792454</v>
+        <v>0.3874267869437278</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7315266803331284</v>
+        <v>0.3925601668999998</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6324362647882658</v>
+        <v>0.3925601668999991</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5862784234552012</v>
+        <v>0.3925601668999955</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3763281536602175</v>
+        <v>0.3925601668999766</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3796352427385145</v>
+        <v>0.3925601668998784</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3514905684279914</v>
+        <v>0.392560166899369</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3436730814091082</v>
+        <v>0.3925601668967239</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3348289715075891</v>
+        <v>0.3925601668829917</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3331893234998242</v>
+        <v>0.3925601668116988</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>0.333947974545635</v>
+        <v>0.3925601664415675</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3344172645781615</v>
+        <v>0.3925601645199622</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>0.3350769404617849</v>
+        <v>0.3925601545435873</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>0.3353766193246073</v>
+        <v>0.3925601027493684</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>0.3353746917663612</v>
+        <v>0.3925598338500667</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>0.3355154467042921</v>
+        <v>0.3925584378117362</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3357487890335164</v>
+        <v>0.3925511900938659</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3433100674593284</v>
+        <v>0.3925135642851064</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3344592131218199</v>
+        <v>0.3923182788524134</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3230732241042686</v>
+        <v>0.3913059253723687</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3198989150893806</v>
+        <v>0.3860904133926276</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3302405053998392</v>
+        <v>0.3600564651505179</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>0.4050345750712405</v>
+        <v>0.2480510833501829</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2784337529939935</v>
+        <v>-0.03719290026168892</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7572079601207087</v>
+        <v>-0.3008142716812418</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>0.9956878531071215</v>
+        <v>-0.3937170648816554</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>1.126121971149564</v>
+        <v>-0.4145467869437278</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模型生成（非实测）</t>
+          <t>标准双支路模型生成（非实测）</t>
         </is>
       </c>
     </row>
@@ -1149,55 +1149,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.8122403338（保持前次角度模型）</t>
+          <t>0.8122403338</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>开关阈值Ic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
+          <t>±0.02640192 A（平滑角度模型）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>形状插值</t>
+          <t>开关宽度</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45°→75°线性混合</t>
+          <t>0.00170000 A（窄开关区）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>纵轴单位</t>
+          <t>曲线结构</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>原始文件未注明，保留原始数值尺度</t>
+          <t>支路1在+Ic由低平台翻到高平台；支路2在−Ic由高平台翻到低平台</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>噪声处理</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>未添加随机噪声；未使用原始回线端点噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>实测区分</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>本文件是模型预测/标准化数据，不是该角度的原始实测记录</t>
         </is>
       </c>
     </row>
